--- a/songs/DancingOnMyOwnIntro_v1/quelle/struktur.xlsx
+++ b/songs/DancingOnMyOwnIntro_v1/quelle/struktur.xlsx
@@ -441,17 +441,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,7 +466,7 @@
           <t>Robyn</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Vorspann (alter Code in src/songs.cpp, Song #81): kein Schluss-Black,</t>
         </is>
@@ -480,7 +481,7 @@
       <c r="C2" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>am Ende Sprung nach Song #8 Dancing On My Own, Part 'chorus 1' (GEN_DANCINGONMYOWN_CHORUS_1).</t>
         </is>
@@ -495,7 +496,7 @@
       <c r="C3" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Die Takte sind aus den ms des alten Codes gerechnet (Einspieler, nicht im Taktraster).</t>
         </is>
@@ -534,20 +535,25 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Beschreibung</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -569,16 +575,21 @@
         </is>
       </c>
       <c r="D6" s="7" t="n"/>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Schwarz bleibt; zwei bis vier kurze starke Blinder auf markante Schläge des Einspielers (Takt als Zwischenzeile eintragen), der letzte klingt lang über 2 Takte aus.</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Einspieler läuft, alles dunkel</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>progBlack(10000, 1)</t>
         </is>
@@ -600,16 +611,21 @@
         </is>
       </c>
       <c r="D7" s="7" t="n"/>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Lauftext "Nerds on Fire" bleibt. Dazu Feuer-Impulse, die zwischen Lampe 1 und Lampe 2 hin und her springen (wie in #80) - das Erkennungszeichen aller Vorspanne.</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>nur Matrix: Lauftext, alle anderen Geräte schwarz (2 Durchläufe)</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>progBlack(23400, 2)   (Matrix: progScrollText("Nerds on Fire", 23400, 90, getRandomColor(), 2))</t>
         </is>
@@ -631,16 +647,21 @@
         </is>
       </c>
       <c r="D8" s="7" t="n"/>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Ab hier Wasserringe als Grundbild auf der Matrix (blenden über 2 Beats ein), übrige Geräte dunkel; ein Blinder auf die 1 von Takt 21, klingt über 1,5 Takte aus.</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>alles dunkel</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>progBlack(10000, 3)</t>
         </is>
@@ -662,16 +683,21 @@
         </is>
       </c>
       <c r="D9" s="7" t="n"/>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Gitarre und Bass beginnen ganz dunkel zu atmen (Szene Calm, BLUE, 20 %), wird bis zum Songtitel heller (fade_in über den Part).</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>alles dunkel</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>progBlack(9836, 4)</t>
         </is>
@@ -693,16 +719,21 @@
         </is>
       </c>
       <c r="D10" s="7" t="n"/>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Statt Lauftext: "DANCING" / "ON MY" / "OWN" als drei Wörter auf der Matrix, je mit Blinder und über 2 Takte ausblendend (wie THE / NERDS / ON in #80), Wasserringe darunter. Der Titel-Lauftext kann dann wie bei #9 beim Einstieg in den Song laufen (trailer_entry).</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>nur Matrix: Lauftext, alle anderen Geräte schwarz</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>progBlack(18000, 5)   (Matrix: progScrollText("Dancing on my own by Robyn", 18000, 90, getRandomColor(), 5))</t>
         </is>
@@ -724,16 +755,21 @@
         </is>
       </c>
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Weißer Strobo statt drei Zufallsfarben; auf der Matrix "OWN" schwarz ausgestanzt über dem Strobo.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Strobo auf allen Geräten, danach direkt in den Chorus</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>progStrobo(1306, 100, 82, getRandomColor(), getRandomColor(), getRandomColor())</t>
         </is>
@@ -753,7 +789,7 @@
           <t>0 sek. BLACK</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>
